--- a/www/download/COUNTRY.IRL.rpA2.xlsx
+++ b/www/download/COUNTRY.IRL.rpA2.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>Irlanda</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>0.791728047333354</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>0.793285656462526</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>0.83647008002156</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>0.890583022093105</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>0.938262390790355</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>1.08271976714892</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>1.11656986366326</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>1.05752964034084</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>0.884016998033016</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>0.803923180836867</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>0.80379392216222</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>0.796431997410537</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>0.729660720781679</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.679902076537751</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.716948691519964</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.285</t>
+          <t>2.63118240604316</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.331</t>
+          <t>2.57977422616623</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>2.97214812195759</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1.526</t>
+          <t>3.16758270817669</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.622</t>
+          <t>3.19139893928758</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.697</t>
+          <t>3.14074186531755</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.748</t>
+          <t>2.6897555773058</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1.779</t>
+          <t>2.4894711543649</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.814</t>
+          <t>2.75118123917623</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1.871</t>
+          <t>2.94054695167228</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1.962</t>
+          <t>2.55082221355463</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2.048</t>
+          <t>2.35494206984538</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2.123</t>
+          <t>2.07807778261848</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2.177</t>
+          <t>2.01095267112013</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2.002</t>
+          <t>1.75164255471035</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.018</t>
+          <t>0.953016376241808</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.063</t>
+          <t>0.898999155286363</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.122</t>
+          <t>1.14385968936815</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.224</t>
+          <t>1.23749760623584</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.311</t>
+          <t>1.22873229985951</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.381</t>
+          <t>1.1987328317418</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.432</t>
+          <t>1.00424884895346</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1.461</t>
+          <t>0.889214476672416</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.494</t>
+          <t>1.05846277061869</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1.541</t>
+          <t>1.1434897464261</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.10581107899543</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1.714</t>
+          <t>1.19439807447079</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>1.762</t>
+          <t>1.01448377938534</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>0.845748211897202</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.585</t>
+          <t>0.632480043326047</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2547.899</t>
+          <t>-0.106440970590365</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2653.568</t>
+          <t>-0.104352912683498</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2769.255</t>
+          <t>0.0394749718063809</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2978.043</t>
+          <t>0.1084138630992</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>3146.232</t>
+          <t>0.122701522911573</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3278.661</t>
+          <t>0.129339965165495</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3360.912</t>
+          <t>0.0389463090290227</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3387.924</t>
+          <t>-0.0141522167536656</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>3426.525</t>
+          <t>0.05283011287775</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>3525.15</t>
+          <t>0.10146165447261</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>3696.057</t>
+          <t>-0.0217362508136407</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>3837.868</t>
+          <t>0.0913769577359573</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>3943.674</t>
+          <t>-0.111432526446196</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>3993.21</t>
+          <t>-0.168014693544288</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>3609.214</t>
+          <t>-0.264516850859234</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1929.917</t>
+          <t>10094805454.4852</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2034.51</t>
+          <t>10575497442.9686</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2130.014</t>
+          <t>10476616783.8028</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2308.418</t>
+          <t>10608812395.5349</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2458.008</t>
+          <t>11786540881.4265</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2578.571</t>
+          <t>12556439349.1927</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2667.309</t>
+          <t>12926861705.9664</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2691.109</t>
+          <t>12549997311.7512</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2729.001</t>
+          <t>13565445821.0382</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2809.265</t>
+          <t>14906048076.7044</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2977.279</t>
+          <t>15788781701.5776</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>3109.725</t>
+          <t>16610493251.9308</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>3164.381</t>
+          <t>17551133431.8373</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>3056.794</t>
+          <t>16196068253.2238</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2739.318</t>
+          <t>15019635678.5275</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>22.86</t>
+          <t>2564960598.84275</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>24.37</t>
+          <t>2765999225.93859</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>2562247561.56878</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>26.39</t>
+          <t>2648307825.29726</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>2819835218.62985</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>2985345085.33351</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>29.28</t>
+          <t>3418575484.79325</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>3692284193.40849</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>33.1</t>
+          <t>3498306962.86072</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>34.89</t>
+          <t>3463682059.36992</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>36.56</t>
+          <t>3976622317.16322</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>40.99</t>
+          <t>4151332138.97484</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>41.01</t>
+          <t>4746327823.60421</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>42.42</t>
+          <t>4894879611.64096</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>45.29</t>
+          <t>4969481581.34418</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>2754551.1665793</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>43.78</t>
+          <t>2656606.01425481</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>44.99</t>
+          <t>2508370.96876147</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>44.88</t>
+          <t>2498000.97779273</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>2596826.77785069</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>44.31</t>
+          <t>2704666.29775386</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>43.42</t>
+          <t>2615930.98326735</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>42.98</t>
+          <t>2368128.90816484</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>2007864.64381653</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>40.79</t>
+          <t>1859315.14840681</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>38.68</t>
+          <t>1776163.43320658</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>37.82</t>
+          <t>1630596.47032836</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>37.03</t>
+          <t>1511850.38340856</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>36.3</t>
+          <t>1450775.54758396</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>35.84</t>
+          <t>1645646.73499942</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>16991.0201637106</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>18095.2784197678</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>30.02</t>
+          <t>18386.5127676131</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>19324.9804419858</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>21261.2576545628</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>22326.5482960189</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>27.3</t>
+          <t>22238.4331679564</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>25.97</t>
+          <t>23236.7923106998</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>24.74</t>
+          <t>25772.7388774672</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>24.33</t>
+          <t>29329.1067525361</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>24.76</t>
+          <t>33123.440429492</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>21.19</t>
+          <t>36777.9734273753</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>42759.1318579785</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>21.28</t>
+          <t>48836.3477004692</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>18.87</t>
+          <t>43194.1108637666</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>41.13</t>
+          <t>44035.0488328386</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>42.76</t>
+          <t>45991.0213391292</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>42.92</t>
+          <t>44809.9215846551</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>44.59</t>
+          <t>44816.061167997</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>46.09</t>
+          <t>51371.6384085972</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>46.85</t>
+          <t>55039.4119669865</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>47.93</t>
+          <t>54660.4103354573</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>50.09</t>
+          <t>53749.0735806622</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>52.43</t>
+          <t>62203.18755399</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>54.93</t>
+          <t>74133.0393607114</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>55.62</t>
+          <t>83522.2973353305</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>57.32</t>
+          <t>91452.9846377247</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>58.63</t>
+          <t>108327.87273937</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>60.21</t>
+          <t>109200.93425667</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>62.76</t>
+          <t>93603.1317556674</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>42.85</t>
+          <t>1.15986209597812</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>1.17445736718002</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>1.4602573424597</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>42.01</t>
+          <t>1.60245213791576</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>41.03</t>
+          <t>1.63306797661556</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>40.29</t>
+          <t>1.61572057347105</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>39.18</t>
+          <t>1.38838036526565</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>1.31449908900932</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>36.34</t>
+          <t>1.53834895501998</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>34.38</t>
+          <t>1.68942180703257</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>34.13</t>
+          <t>1.51666282874503</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>33.21</t>
+          <t>1.56737025474678</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>32.53</t>
+          <t>1.33533022909171</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>31.42</t>
+          <t>1.26630331054188</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>29.91</t>
+          <t>1.10146970343049</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>16.02</t>
+          <t>10514.200186931</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>14.54</t>
+          <t>11044.4194937954</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>13.98</t>
+          <t>11151.7031242688</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>11305.0612827041</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>12.88</t>
+          <t>11683.5268741575</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>12.86</t>
+          <t>10878.212509104</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>10639.0917351734</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>11655.9578944585</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>11.23</t>
+          <t>14520.3084097658</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>10.69</t>
+          <t>16623.8437844044</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>10.25</t>
+          <t>18821.696288396</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>21012.9477639421</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>27072.505507697</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>8.37</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.791728047333354</t>
+          <t>2520.58790802181</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.793285656462526</t>
+          <t>2601.39336721533</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.83647008002156</t>
+          <t>2283.4360650567</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.890583022093105</t>
+          <t>2163.93128298305</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.938262390790355</t>
+          <t>2151.5589186938</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.08271976714892</t>
+          <t>2161.2015462118</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.11656986366326</t>
+          <t>2387.7619406717</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.05752964034084</t>
+          <t>2526.94368292753</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.884016998033016</t>
+          <t>2341.25775709761</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.803923180836867</t>
+          <t>2247.39443729844</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.80379392216222</t>
+          <t>2439.98240073827</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.796431997410537</t>
+          <t>2422.08332617142</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.729660720781679</t>
+          <t>2693.90418491428</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.679902076537751</t>
+          <t>2829.53448338827</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.716948691519964</t>
+          <t>3135.37499800891</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>3816828716.42445</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>4271383081.373</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>4435413600.58725</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>4997549167.53571</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>6420322251.38868</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>6938535406.34105</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>8560792053.63737</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>10544021160.212</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>11575399686.092</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>12043250360.8071</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>11463459644.2481</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>10704937884.7165</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>11407078983.1881</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>10521091273.4256</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>12401686709.8012</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>5113196996.57113</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>5774823381.43325</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>5949970191.65257</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>7570429303.78549</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>9477395358.55397</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>10642890500.6094</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>12274512624.3884</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>14900761461.9337</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>15791021200.1213</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>16032653282.7864</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>14695330748.7734</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>13197914619.7188</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>12608185668.7376</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>12345426189.8911</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>14347052904.9261</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>-1296368280.14667</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>-1503440300.06025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>-1514556591.06532</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>-2572880136.24977</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>-3057073107.16529</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>-3704355094.26837</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>-3713720570.75107</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.207</t>
+          <t>-4356740301.72169</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>-4215621514.02938</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.329</t>
+          <t>-3989402921.97933</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.371</t>
+          <t>-3231871104.52521</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.436</t>
+          <t>-2492976735.00226</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-1201106685.5495</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1824334916.46541</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1945366195.12493</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>5444.1222821171</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>5656.61897227463</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>5617.84034509303</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>5631.52759370203</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>5665.20088861426</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.206</t>
+          <t>5653.09934784366</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.225</t>
+          <t>5702.88373602888</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>5848.60885211363</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.319</t>
+          <t>5942.92918116114</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>6044.19160867412</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.417</t>
+          <t>6140.61301073006</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.464</t>
+          <t>6218.38468613065</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.551</t>
+          <t>6291.15587730697</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.562</t>
+          <t>6412.58336699525</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.482</t>
+          <t>6588.89556720916</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>5354.81207369039</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>5568.65769349077</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>5531.97402805192</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>5562.62790970473</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>5609.92659211372</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>5617.10429606064</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>5655.64296605121</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>5787.96649364028</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>5900.59061205391</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>6010.56853986876</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>6107.01442236737</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>6204.16962517389</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.228</t>
+          <t>6277.95943279584</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>6408.69171745056</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.202</t>
+          <t>6571.16801773242</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>263.12</t>
+          <t>47267.1435503917</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>257.98</t>
+          <t>52335.3517922755</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>297.21</t>
+          <t>58755.980409501</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>316.76</t>
+          <t>67689.9588631831</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>319.14</t>
+          <t>79579.0265480544</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>314.07</t>
+          <t>88633.6395201882</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>268.98</t>
+          <t>96846.7936380043</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>248.95</t>
+          <t>104885.773008976</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>275.12</t>
+          <t>125481.444754296</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>294.05</t>
+          <t>149748.221083719</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>255.08</t>
+          <t>159911.93169149</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>235.49</t>
+          <t>170932.367972707</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>207.81</t>
+          <t>202338.860603665</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>201.1</t>
+          <t>213772.943765359</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>175.16</t>
+          <t>195689.115276211</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>3920867576.88598</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>89.9</t>
+          <t>3928694925.23238</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>114.39</t>
+          <t>3849880180.26723</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>123.75</t>
+          <t>3799692358.78742</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>122.87</t>
+          <t>4542564723.28868</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>119.87</t>
+          <t>4956232255.24925</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>100.42</t>
+          <t>4879243608.75496</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>4456416690.70492</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>105.85</t>
+          <t>4725526010.14258</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>114.35</t>
+          <t>5562017999.54948</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>110.58</t>
+          <t>5588202399.97978</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>119.44</t>
+          <t>5418504677.82823</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>101.45</t>
+          <t>5617465254.94076</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>84.57</t>
+          <t>5043265658.46449</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>63.25</t>
+          <t>4389148809.92218</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-10.64</t>
+          <t>37802.9525057756</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-10.44</t>
+          <t>41997.3925849796</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>46212.1216525593</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>10.84</t>
+          <t>55125.4373668695</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>12.27</t>
+          <t>63494.400704881</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>12.93</t>
+          <t>72614.740911448</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>77624.1208204714</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>80475.6649472791</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>96366.1927540968</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>117771.706854291</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>131133.924261323</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>143958.75462874</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>-11.14</t>
+          <t>171829.484913713</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>-16.8</t>
+          <t>181990.362949974</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>-26.45</t>
+          <t>154971.787825277</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>6881.716</t>
+          <t>5016008471.75676</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>7412.791</t>
+          <t>5290362624.44316</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>7775.129</t>
+          <t>5001493442.88955</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>8489.872</t>
+          <t>5296716187.22829</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>9097.337</t>
+          <t>6309120694.53401</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>9532.529</t>
+          <t>7159178620.00259</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>9886.358</t>
+          <t>7419663533.37842</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>10298.095</t>
+          <t>7368834028.20923</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>10706.563</t>
+          <t>7680116891.15235</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>11243.406</t>
+          <t>8826855597.35845</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>11984.252</t>
+          <t>9693641598.16319</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>12703.664</t>
+          <t>9785140831.04102</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>13328.12</t>
+          <t>10659772391.0718</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>13950.802</t>
+          <t>9567510584.54527</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>13153.331</t>
+          <t>8223429403.64734</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>5539.961</t>
+          <t>9464.19104461608</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>6014.547</t>
+          <t>10337.9592072959</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>6303.788</t>
+          <t>12543.8587569417</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>6892.094</t>
+          <t>12564.5214963136</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>7424.818</t>
+          <t>16084.6258431734</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>7808.829</t>
+          <t>16018.8986087402</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>8164.859</t>
+          <t>19222.6728175329</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>8545.788</t>
+          <t>24410.1080616971</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>8879.924</t>
+          <t>29115.2520001989</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>9315.302</t>
+          <t>31976.5142294279</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>10007.818</t>
+          <t>28778.0074301669</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>10658.007</t>
+          <t>26973.6133439669</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>11084.243</t>
+          <t>30509.3756899523</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>11093.282</t>
+          <t>31782.5808153854</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>10443.215</t>
+          <t>40717.3274509348</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>10094.805</t>
+          <t>-1095140894.87078</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>10575.497</t>
+          <t>-1361667699.21078</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>10476.617</t>
+          <t>-1151613262.62232</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>10608.812</t>
+          <t>-1497023828.44087</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>11786.541</t>
+          <t>-1766555971.24532</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>12556.439</t>
+          <t>-2202946364.75333</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>12926.862</t>
+          <t>-2540419924.62345</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>12549.997</t>
+          <t>-2912417337.50431</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>13565.446</t>
+          <t>-2954590881.00977</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>14906.048</t>
+          <t>-3264837597.80897</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>15788.782</t>
+          <t>-4105439198.18341</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>16610.493</t>
+          <t>-4366636153.21278</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>17551.133</t>
+          <t>-5042307136.13108</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>16196.068</t>
+          <t>-4524244926.08078</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>15019.636</t>
+          <t>-3834280593.72516</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>35628.71028</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>38229.90603</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>41540.18573</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>46418.20626</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>50019.52065</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>48963.72501</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>52428.545</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>61114.62804</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>74132.09013</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>84365.43219</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>87903.43056</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>95997.10793</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>110084.02041</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>111640.89857</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>99658.50712</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>3895.103</t>
+          <t>0.0729840454392032</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>4160.955</t>
+          <t>0.0835338898215211</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>4298.79</t>
+          <t>0.102213453290353</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>4574.59</t>
+          <t>0.125557931722302</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>4878.113</t>
+          <t>0.141174537540964</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>5093.476</t>
+          <t>0.159660952077967</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>5259.257</t>
+          <t>0.177083898526582</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>5425.613</t>
+          <t>0.196765951483505</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>5620.591</t>
+          <t>0.190329076055617</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>5897.25</t>
+          <t>0.177203258064592</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>6261.547</t>
+          <t>0.160724496978183</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>6679.938</t>
+          <t>0.150805399370741</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>6927.776</t>
+          <t>0.128489329984444</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>7243.132</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>6930.963</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>30216.7274515467</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>32858.690471087</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>34730.506188777</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>36928.6783913506</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>39231.0631348185</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>38677.4118061508</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>41788.0281601937</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>47294.7074669603</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>61157.1850026985</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>73200.7446860464</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>82179.909290841</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>91298.543601515</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>107930.941673357</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>123709.969852541</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>106941.324329402</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2564.961</t>
+          <t>37408.3853721165</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2765.999</t>
+          <t>40364.5939571423</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2562.248</t>
+          <t>42672.3483138855</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2648.308</t>
+          <t>45441.7179008546</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2819.835</t>
+          <t>48009.4451438283</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2985.345</t>
+          <t>47248.0235749582</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3418.575</t>
+          <t>50629.6601011787</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>3692.284</t>
+          <t>57285.7035400332</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>3498.307</t>
+          <t>73950.0882721045</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>3463.682</t>
+          <t>88451.5230381879</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>3976.622</t>
+          <t>98405.7780784118</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>4151.332</t>
+          <t>108777.262988193</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>4746.328</t>
+          <t>130100.676925427</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>4894.88</t>
+          <t>148319.207223746</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>4969.482</t>
+          <t>127815.480017101</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>115.99</t>
+          <t>165791.087053843</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>117.45</t>
+          <t>178033.329237241</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>146.03</t>
+          <t>181733.881635705</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>160.25</t>
+          <t>185067.896370213</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>163.31</t>
+          <t>186982.497140142</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>161.57</t>
+          <t>177753.198114959</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>138.84</t>
+          <t>184456.723820911</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>131.45</t>
+          <t>207323.147820766</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>153.83</t>
+          <t>272207.674054964</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>168.94</t>
+          <t>329071.438269788</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>151.67</t>
+          <t>370978.698109013</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>156.74</t>
+          <t>435573.725423319</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>133.53</t>
+          <t>549546.964525575</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>126.63</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>110.15</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2.755</t>
+          <t>37408.3853721165</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2.657</t>
+          <t>39586.9000935393</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2.508</t>
+          <t>42636.3199305665</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2.498</t>
+          <t>44339.1547181014</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2.597</t>
+          <t>47127.5998055457</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2.705</t>
+          <t>48888.9411973636</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2.616</t>
+          <t>50252.7586167629</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2.368</t>
+          <t>51375.7154083659</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2.008</t>
+          <t>52545.289767832</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1.859</t>
+          <t>55553.730422125</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1.776</t>
+          <t>58875.9240749664</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>1.631</t>
+          <t>61543.1947969549</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>1.512</t>
+          <t>67220.7681768881</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1.451</t>
+          <t>73453.1812739769</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>1.646</t>
+          <t>71293.6854282151</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>30216.7274515467</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>31981.71564716</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>34132.6468725914</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>35349.3904568689</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>37589.0812415935</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>39094.8874637977</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>40432.839510253</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>41172.2473951654</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>42185.0981845677</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>44788.0933941631</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>48212.8678112792</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>50722.3678438831</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>54977.3136530097</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>59860.5071632062</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>56684.3282598564</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>22614.3044178835</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>25916.2360028577</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>29727.3507461145</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>34541.8035791454</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>38080.6944361717</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>39258.4573550418</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>43303.4074988213</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>52450.0943399668</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>66329.3435078955</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>74936.3747818121</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>78447.0609315882</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>86699.8173818071</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>97683.4267745733</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>86698.7595662541</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>74385.0519628989</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>5539961175.11778</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>6014547394.4564</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>6303788376.54905</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>6892094361.80388</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>7424817813.50702</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>7808828558.61755</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>8164858565.0587</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>8545788402.00746</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>8879923823.51663</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>9315302063.09694</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>10007817569.5626</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>10658006651.1783</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>11084242843.642</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>11093281868.5659</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>10443214984.9506</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>6881715620.60314</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>7412791081.24025</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>7775128644.71266</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>8489871845.1403</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>9097337458.10121</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>9532529314.04689</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>9886357998.09175</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>10298094684.6471</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>10706562659.6657</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>11243405574.0897</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>11984252427.0932</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>12703663928.6757</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>13328120431.7444</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>13950801878.7666</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>13153331250.006</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>3895102823.13994</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>4160955010.04332</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>4298790121.57756</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>4574589705.4159</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>4878113494.12028</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>5093476465.99016</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>5259257081.2274</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>5425613161.41313</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>5620591269.51637</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>5897250120.46106</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>6261546758.54725</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>6679938132.74748</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>6927775924.06425</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>7243132359.43455</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>6930962634.08325</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1285146.05664965</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1331163</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1405489</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1526234</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1621650</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>1697054</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1748052</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>1779225</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>1814490</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>1870606</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>1962375</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>2047601</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>2123002</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>2176856.4465005</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>2001673.25116501</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1017604.10366158</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1063276.0353731</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1122101.73114926</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1223841</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1310600.97593877</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>1381335.80857661</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1431707</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>1461166</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>1494199.83863608</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>1541199</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>1629775</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>1713951</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>1761877</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>1729924</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1584972</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2547899286.28545</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2653568154.19399</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2769255347.01174</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2978042757.53249</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>3146232450.2526</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>3278660739.29116</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>3360911560.89258</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>3387924434.28586</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>3426524671.01494</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>3525150168.57143</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>3696056554.17269</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>3837868146.12786</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>3943673918.4152</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>3993210073.6081</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>3609213724.27385</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1929917147.60251</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2034509849.31277</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2130014101.6263</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2308418033.48914</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2458008026.38916</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2578571039.99907</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2667309175.65362</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2691108649.85751</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2729000750.27981</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2809265001.64934</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2977278513.48593</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>3109725073.94992</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>3164381155.58501</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>3056793726.46356</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>2739317842.58637</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.228551949077892</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.243723137843603</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.249858280534478</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.263939145793767</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.276483269509155</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.28420368499428</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.292821454861932</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.310523354271164</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.331000979590364</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.348869083619875</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.365645356771562</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.409887125460397</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.41008319108744</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.42418374560626</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.452934382739975</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.420987678638385</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.437758976405333</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.449934012124202</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.448791732503489</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.446990165169487</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.443127372849649</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.434154610173299</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.429782298577874</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.421636914152267</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.407857989703823</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.38679683229293</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.378179481889638</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.370278519530993</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.362968876895351</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.358388550232721</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.350460372283722</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.318517885751064</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.300207707341319</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.287269121702744</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.276526565321358</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.272668942156071</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.273023934964769</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.259694347150962</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.247362106257369</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.243272926676302</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.247557810935509</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.211933392649964</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.219638289381567</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.212847377498389</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.188677067027303</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.41132230650555</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.427637073771549</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.429194920010672</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.445920525466983</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.460949134456281</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.468503566272838</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.479260270875987</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.500930943286282</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.524329133556936</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.549304944270521</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.556246259500836</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.573232942758362</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.586308994149082</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.602086237445446</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.627644332434433</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.428464436081877</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.427003031213508</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.430957855872728</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.420055005105466</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.410277061491551</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.402898681511019</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.39175902868817</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.377963162359787</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.363383196416057</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.343776242687223</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.341260703375215</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.332075520686761</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.325329795878304</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.314234256124497</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.299144275317575</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.160213257412573</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.145359895014944</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.1398472241166</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.134024469427551</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.128773804052169</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.128597752216144</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.128980700435843</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.121105894353931</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.112287670027007</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.106918813042256</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.102493037123948</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.0946915365548767</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.0883612099726135</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.0836795064300565</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.0732113922479913</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>134723.39307</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>149876.90979</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>164938.59555</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>178120.27518</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>195301.38045</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>206241.77683</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>224824.28026</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>249407.63682</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>318780.68156</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>379865.20657</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>417431.60801</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>463706.59768</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>550941.06294</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>561762.81601</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>482054.72113</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>60022.68979</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>66280.82996</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>72399.69906</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>79983.52148</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>86090.13958</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>86506.48093</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>93933.0676</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>109735.79788</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>140279.43178</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>163387.89782</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>176852.83901</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>195477.08037</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>227784.1037</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>235017.96679</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>202200.53198</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>131261.45336144</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>136759.567012045</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>144311.489342752</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>154908.383914814</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>169219.619632582</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>186069.652263705</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>203826.797026311</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>223182.255285232</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>244092.347013215</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>268622.229508064</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>299043.02653643</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>329852.481077754</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>361935.230409352</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA2</t>
